--- a/giveaway_forms/032_paranormal_giveaway_entry_form--giveaway_forms.xlsx
+++ b/giveaway_forms/032_paranormal_giveaway_entry_form--giveaway_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1100,17 +1100,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>favorite_paranormal_genre_choices</t>
+          <t>how_entered_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>science_fiction</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Science fiction</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>online_event</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Online event</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>online_event</t>
+          <t>online_ad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Online event</t>
+          <t>Online ad</t>
         </is>
       </c>
     </row>
@@ -1173,29 +1173,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>online_ad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Online ad</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_entered_choices</t>
+          <t>prize_preferred_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Gift Card</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gift_card</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gift Card</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>experiential</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Experiential</t>
         </is>
       </c>
     </row>
@@ -1258,29 +1258,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>experiential</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Experiential</t>
+          <t>Experience</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prize_preferred_choices</t>
+          <t>prize_category_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>paranormal_book</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Paranormal book</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>paranormal_book</t>
+          <t>paranormal_movie</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paranormal book</t>
+          <t>Paranormal movie</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>paranormal_movie</t>
+          <t>paranormal_tv_show</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Paranormal movie</t>
+          <t>Paranormal TV show</t>
         </is>
       </c>
     </row>
@@ -1326,27 +1326,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>paranormal_tv_show</t>
+          <t>paranormal_video_game</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Paranormal TV show</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>prize_category_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>paranormal_video_game</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Paranormal video game</t>
         </is>
